--- a/output/yearly_benthic_cover_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_44_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.25226674421549</v>
+        <v>45.57021772763912</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0056119314387</v>
+        <v>98.81989387067733</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0574923330102</v>
+        <v>87.92126502156893</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95099213096695</v>
+        <v>45.84317850704044</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228791104182497</v>
+        <v>2.228523207754828</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720703763906487</v>
+        <v>5.651857351819652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429303680608325</v>
+        <v>0.7428410692516095</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9805591346248</v>
+        <v>33.94452304625181</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17479693079829</v>
+        <v>34.17068918557403</v>
       </c>
       <c r="I3" t="n">
-        <v>6.566396231057112</v>
+        <v>6.54007447809443</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643314800380203</v>
+        <v>4.642756682822559</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94250766698979</v>
+        <v>12.07873497843107</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87080664713864</v>
+        <v>48.84330953018885</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643064450954</v>
+        <v>106.7652230156604</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.04860290349386</v>
+        <v>86.9235784451901</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57609441779395</v>
+        <v>42.47840177621216</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179730973134755</v>
+        <v>2.179920258844079</v>
       </c>
       <c r="E4" t="n">
-        <v>6.508694155331427</v>
+        <v>6.438839315537287</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444903582142184</v>
+        <v>0.74439684544079</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23257935262917</v>
+        <v>33.20421039719538</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24655647785404</v>
+        <v>34.24225489027634</v>
       </c>
       <c r="I4" t="n">
-        <v>5.483486847491378</v>
+        <v>5.461476453891292</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653064738838865</v>
+        <v>4.652480284004937</v>
       </c>
       <c r="K4" t="n">
-        <v>12.95139709650616</v>
+        <v>13.07642155480993</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29010859039275</v>
+        <v>44.26350793347528</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81760010469287</v>
+        <v>99.81833126449736</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.82100218474358</v>
+        <v>85.735510265575</v>
       </c>
       <c r="C5" t="n">
-        <v>42.1994895160442</v>
+        <v>42.13783703377625</v>
       </c>
       <c r="D5" t="n">
-        <v>2.119662533019763</v>
+        <v>2.121749507379198</v>
       </c>
       <c r="E5" t="n">
-        <v>7.092278825252114</v>
+        <v>7.026903128617128</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458140634662288</v>
+        <v>0.7457163792131691</v>
       </c>
       <c r="G5" t="n">
-        <v>32.31676486574354</v>
+        <v>32.3181624499062</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30744691944653</v>
+        <v>34.30295344380578</v>
       </c>
       <c r="I5" t="n">
-        <v>4.577697081151467</v>
+        <v>4.559297986571219</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661337896663931</v>
+        <v>4.660727370082307</v>
       </c>
       <c r="K5" t="n">
-        <v>14.17899781525644</v>
+        <v>14.264489734425</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46919358960239</v>
+        <v>43.44596555252402</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84768092090303</v>
+        <v>99.84829232072526</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.44839564989078</v>
+        <v>84.30462020189407</v>
       </c>
       <c r="C6" t="n">
-        <v>41.53770501389989</v>
+        <v>41.41487723290299</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052694306824921</v>
+        <v>2.051616624040957</v>
       </c>
       <c r="E6" t="n">
-        <v>7.504956727497958</v>
+        <v>7.428822513244143</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469387672270353</v>
+        <v>0.7468383219599513</v>
       </c>
       <c r="G6" t="n">
-        <v>31.29575497114894</v>
+        <v>31.2499091481273</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35918329244362</v>
+        <v>34.35456281015775</v>
       </c>
       <c r="I6" t="n">
-        <v>3.820500289579328</v>
+        <v>3.805131272114281</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668367295168972</v>
+        <v>4.667739512249695</v>
       </c>
       <c r="K6" t="n">
-        <v>15.55160435010924</v>
+        <v>15.69537979810593</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78353238373668</v>
+        <v>42.76309580269743</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8728417477458</v>
+        <v>99.87335283370635</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.8585747470254</v>
+        <v>82.67512507058262</v>
       </c>
       <c r="C7" t="n">
-        <v>40.54114891005284</v>
+        <v>40.37618193052123</v>
       </c>
       <c r="D7" t="n">
-        <v>1.975343188352399</v>
+        <v>1.97205902324757</v>
       </c>
       <c r="E7" t="n">
-        <v>7.753455029286497</v>
+        <v>7.669914574024032</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478966709861418</v>
+        <v>0.747794358446139</v>
       </c>
       <c r="G7" t="n">
-        <v>30.11644559107628</v>
+        <v>30.03809999835572</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40324686536252</v>
+        <v>34.39854048852239</v>
       </c>
       <c r="I7" t="n">
-        <v>3.187833208298172</v>
+        <v>3.175001887698421</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674354193663387</v>
+        <v>4.673714740288369</v>
       </c>
       <c r="K7" t="n">
-        <v>17.1414252529746</v>
+        <v>17.32487492941736</v>
       </c>
       <c r="L7" t="n">
-        <v>42.2113008289287</v>
+        <v>42.19324504916935</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89387499195614</v>
+        <v>99.89430190910794</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.71968953167281</v>
+        <v>87.56183281743384</v>
       </c>
       <c r="C8" t="n">
-        <v>42.82097755956059</v>
+        <v>42.67102638328367</v>
       </c>
       <c r="D8" t="n">
-        <v>1.979580791920967</v>
+        <v>1.976295357055423</v>
       </c>
       <c r="E8" t="n">
-        <v>9.572133356214755</v>
+        <v>9.49853967575649</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749501095787148</v>
+        <v>0.7494007538352535</v>
       </c>
       <c r="G8" t="n">
-        <v>30.61162398726316</v>
+        <v>30.53845555673773</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4770504062088</v>
+        <v>34.47243467642166</v>
       </c>
       <c r="I8" t="n">
-        <v>5.645418045608313</v>
+        <v>5.642952086156947</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684381848669676</v>
+        <v>4.683754711470335</v>
       </c>
       <c r="K8" t="n">
-        <v>12.28031046832717</v>
+        <v>12.43816718256617</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71093420072236</v>
+        <v>44.70311123397791</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81222222861012</v>
+        <v>99.81230479982776</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.74560683840235</v>
+        <v>85.47131740697789</v>
       </c>
       <c r="C9" t="n">
-        <v>41.72284237758337</v>
+        <v>41.45591927822855</v>
       </c>
       <c r="D9" t="n">
-        <v>1.890354247875337</v>
+        <v>1.881408378286964</v>
       </c>
       <c r="E9" t="n">
-        <v>9.926206696793669</v>
+        <v>9.827673887756671</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750874343845182</v>
+        <v>0.7507776297017543</v>
       </c>
       <c r="G9" t="n">
-        <v>29.23185235725188</v>
+        <v>29.07222644594777</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54021981687837</v>
+        <v>34.53577096628069</v>
       </c>
       <c r="I9" t="n">
-        <v>4.713134726725528</v>
+        <v>4.711099913368078</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69296464903239</v>
+        <v>4.692360185635965</v>
       </c>
       <c r="K9" t="n">
-        <v>14.25439316159765</v>
+        <v>14.5286825930221</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8659472928854</v>
+        <v>43.85864945968945</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84318283206642</v>
+        <v>99.84325133094009</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.54586794378035</v>
+        <v>83.21875945246325</v>
       </c>
       <c r="C10" t="n">
-        <v>40.25415079652259</v>
+        <v>39.93384781959075</v>
       </c>
       <c r="D10" t="n">
-        <v>1.791860193951755</v>
+        <v>1.780288231589803</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06464613237727</v>
+        <v>9.954815415180878</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520528469692148</v>
+        <v>0.7519601085434386</v>
       </c>
       <c r="G10" t="n">
-        <v>27.70877082605348</v>
+        <v>27.50968009133655</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59443096058388</v>
+        <v>34.59016499299817</v>
       </c>
       <c r="I10" t="n">
-        <v>3.933776690287153</v>
+        <v>3.932099934417912</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700330293557594</v>
+        <v>4.699750678396492</v>
       </c>
       <c r="K10" t="n">
-        <v>16.45413205621967</v>
+        <v>16.78124054753675</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16079673818204</v>
+        <v>43.15404774639006</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86907959092429</v>
+        <v>99.86913611351756</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.23961614782739</v>
+        <v>80.88583563125181</v>
       </c>
       <c r="C11" t="n">
-        <v>38.5574360770498</v>
+        <v>38.20994501633058</v>
       </c>
       <c r="D11" t="n">
-        <v>1.689685751616813</v>
+        <v>1.676722375759323</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03783929529262</v>
+        <v>9.922570969221518</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530657601930036</v>
+        <v>0.7529768984389555</v>
       </c>
       <c r="G11" t="n">
-        <v>26.12877690884113</v>
+        <v>25.90934172380279</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64102496887816</v>
+        <v>34.63693732819195</v>
       </c>
       <c r="I11" t="n">
-        <v>3.282562461799396</v>
+        <v>3.281180720593797</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706661001206275</v>
+        <v>4.706105615243472</v>
       </c>
       <c r="K11" t="n">
-        <v>18.76038385217259</v>
+        <v>19.11416436874821</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57290849604743</v>
+        <v>42.56666561674292</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89072842526983</v>
+        <v>99.89077500182171</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.7796241998355</v>
+        <v>78.5605766533097</v>
       </c>
       <c r="C12" t="n">
-        <v>36.60528722097935</v>
+        <v>36.3920725338074</v>
       </c>
       <c r="D12" t="n">
-        <v>1.581716713294767</v>
+        <v>1.57460475892369</v>
       </c>
       <c r="E12" t="n">
-        <v>9.852872292270783</v>
+        <v>9.774504353947282</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539383948433405</v>
+        <v>0.7538514970621252</v>
       </c>
       <c r="G12" t="n">
-        <v>24.45917715475701</v>
+        <v>24.33138208727287</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68116616279366</v>
+        <v>34.67716886485776</v>
       </c>
       <c r="I12" t="n">
-        <v>2.738638514105063</v>
+        <v>2.737493234607678</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71211496777088</v>
+        <v>4.711571856638282</v>
       </c>
       <c r="K12" t="n">
-        <v>21.2203758001645</v>
+        <v>21.43942334669031</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0831546882506</v>
+        <v>42.07736021059692</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90881770939444</v>
+        <v>99.90885609109463</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.4153863894862</v>
+        <v>76.22848246976903</v>
       </c>
       <c r="C13" t="n">
-        <v>34.66383320510897</v>
+        <v>34.48245590736082</v>
       </c>
       <c r="D13" t="n">
-        <v>1.479005143928854</v>
+        <v>1.473157372782266</v>
       </c>
       <c r="E13" t="n">
-        <v>9.593804123131225</v>
+        <v>9.525347389454684</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754689705974891</v>
+        <v>0.7546042501169229</v>
       </c>
       <c r="G13" t="n">
-        <v>22.87087727156813</v>
+        <v>22.76377910628775</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71572647484498</v>
+        <v>34.71179550537845</v>
       </c>
       <c r="I13" t="n">
-        <v>2.284473007695061</v>
+        <v>2.283522282518197</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716810662343071</v>
+        <v>4.716276563230768</v>
       </c>
       <c r="K13" t="n">
-        <v>23.58461361051381</v>
+        <v>23.77151753023097</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67547989231876</v>
+        <v>41.6699850836691</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92392670794152</v>
+        <v>99.92395852126089</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.31440255068502</v>
+        <v>83.37382773922306</v>
       </c>
       <c r="C14" t="n">
-        <v>39.04735102834655</v>
+        <v>38.85542534288306</v>
       </c>
       <c r="D14" t="n">
-        <v>1.480663881118645</v>
+        <v>1.474970588572871</v>
       </c>
       <c r="E14" t="n">
-        <v>12.01508730823246</v>
+        <v>11.96555902655269</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555361072786267</v>
+        <v>0.7555330445330865</v>
       </c>
       <c r="G14" t="n">
-        <v>24.83985620504216</v>
+        <v>24.70718735700611</v>
       </c>
       <c r="H14" t="n">
-        <v>36.69798967035258</v>
+        <v>36.66990981018276</v>
       </c>
       <c r="I14" t="n">
-        <v>2.803168708169122</v>
+        <v>3.078586384043751</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722100670491419</v>
+        <v>4.722081528331791</v>
       </c>
       <c r="K14" t="n">
-        <v>16.68559744931498</v>
+        <v>16.62617226077692</v>
       </c>
       <c r="L14" t="n">
-        <v>44.17371724187257</v>
+        <v>44.41590900280984</v>
       </c>
       <c r="M14" t="n">
-        <v>99.9066657195341</v>
+        <v>99.89750660646983</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.57436113122375</v>
+        <v>82.73256977376315</v>
       </c>
       <c r="C15" t="n">
-        <v>38.74043106945636</v>
+        <v>38.68717802903477</v>
       </c>
       <c r="D15" t="n">
-        <v>1.45345129877316</v>
+        <v>1.451398906929861</v>
       </c>
       <c r="E15" t="n">
-        <v>12.18396285581307</v>
+        <v>12.20475780547781</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562492335909243</v>
+        <v>0.7563148072099375</v>
       </c>
       <c r="G15" t="n">
-        <v>24.38333353230767</v>
+        <v>24.31473677953524</v>
       </c>
       <c r="H15" t="n">
-        <v>36.73262772641667</v>
+        <v>36.71025072216306</v>
       </c>
       <c r="I15" t="n">
-        <v>2.338178774378974</v>
+        <v>2.568143207385135</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726557709943279</v>
+        <v>4.72696754506211</v>
       </c>
       <c r="K15" t="n">
-        <v>17.42563886877623</v>
+        <v>17.26743022623685</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75606426431828</v>
+        <v>43.9598754562827</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92213420255088</v>
+        <v>99.91448371155433</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.15989991478435</v>
+        <v>80.49319344289914</v>
       </c>
       <c r="C16" t="n">
-        <v>36.68728275604252</v>
+        <v>36.8445185248701</v>
       </c>
       <c r="D16" t="n">
-        <v>1.362255411417946</v>
+        <v>1.367012535647483</v>
       </c>
       <c r="E16" t="n">
-        <v>11.74449816258889</v>
+        <v>11.85215899361136</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568624800131699</v>
+        <v>0.7569856878318265</v>
       </c>
       <c r="G16" t="n">
-        <v>22.85341660971528</v>
+        <v>22.90104382736721</v>
       </c>
       <c r="H16" t="n">
-        <v>36.76241440458087</v>
+        <v>36.74281414099264</v>
       </c>
       <c r="I16" t="n">
-        <v>1.950062346385896</v>
+        <v>2.142017708499703</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730390500082314</v>
+        <v>4.731160548948917</v>
       </c>
       <c r="K16" t="n">
-        <v>19.84010008521562</v>
+        <v>19.50680655710087</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40766774834243</v>
+        <v>43.57733760671278</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93505058960056</v>
+        <v>99.92866268868374</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.92366857032604</v>
+        <v>82.37852209918064</v>
       </c>
       <c r="C17" t="n">
-        <v>37.9784215470427</v>
+        <v>38.20051749933904</v>
       </c>
       <c r="D17" t="n">
-        <v>1.363319141656157</v>
+        <v>1.368202753291588</v>
       </c>
       <c r="E17" t="n">
-        <v>12.54478310346092</v>
+        <v>12.70402403007203</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574534833590982</v>
+        <v>0.7576447730256326</v>
       </c>
       <c r="G17" t="n">
-        <v>23.34252163425313</v>
+        <v>23.40390601098576</v>
       </c>
       <c r="H17" t="n">
-        <v>37.2623804038035</v>
+        <v>37.25772794727252</v>
       </c>
       <c r="I17" t="n">
-        <v>1.919126532798864</v>
+        <v>2.151736753122887</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734084270994366</v>
+        <v>4.735279831410205</v>
       </c>
       <c r="K17" t="n">
-        <v>18.07633142967397</v>
+        <v>17.62147790081938</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88132605216169</v>
+        <v>44.10634243554475</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93607902887835</v>
+        <v>99.92833783570318</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.5881889566933</v>
+        <v>80.19093295971561</v>
       </c>
       <c r="C18" t="n">
-        <v>35.93914310087418</v>
+        <v>36.34504075473264</v>
       </c>
       <c r="D18" t="n">
-        <v>1.278700442150679</v>
+        <v>1.289297822963414</v>
       </c>
       <c r="E18" t="n">
-        <v>12.03287560739743</v>
+        <v>12.2704519162426</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579611743381144</v>
+        <v>0.7582099062304321</v>
       </c>
       <c r="G18" t="n">
-        <v>21.89369445687668</v>
+        <v>22.05419116151534</v>
       </c>
       <c r="H18" t="n">
-        <v>37.28735589708896</v>
+        <v>37.28551878005858</v>
       </c>
       <c r="I18" t="n">
-        <v>1.600344039228219</v>
+        <v>1.794451458765055</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737257339613217</v>
+        <v>4.738811913940201</v>
       </c>
       <c r="K18" t="n">
-        <v>20.41181104330671</v>
+        <v>19.80906704028438</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59573678546359</v>
+        <v>43.78612173961847</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94669092964448</v>
+        <v>99.94022953463549</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.64740958414471</v>
+        <v>79.36068856118816</v>
       </c>
       <c r="C19" t="n">
-        <v>35.24043616681055</v>
+        <v>35.79113577769726</v>
       </c>
       <c r="D19" t="n">
-        <v>1.245055278015247</v>
+        <v>1.260032687558244</v>
       </c>
       <c r="E19" t="n">
-        <v>11.93935441020576</v>
+        <v>12.24131698676831</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583911742523385</v>
+        <v>0.7586864316847162</v>
       </c>
       <c r="G19" t="n">
-        <v>21.31762760083206</v>
+        <v>21.55359395340885</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30850943420963</v>
+        <v>37.30895226283015</v>
       </c>
       <c r="I19" t="n">
-        <v>1.338526847552553</v>
+        <v>1.496316040908394</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739944839077117</v>
+        <v>4.741790198029477</v>
       </c>
       <c r="K19" t="n">
-        <v>21.3525904158553</v>
+        <v>20.63931143881182</v>
       </c>
       <c r="L19" t="n">
-        <v>43.3623811534428</v>
+        <v>43.51970690963633</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95540773610865</v>
+        <v>99.95015412614543</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.02886265494649</v>
+        <v>76.97703458770803</v>
       </c>
       <c r="C20" t="n">
-        <v>32.8277880407117</v>
+        <v>33.63779775828839</v>
       </c>
       <c r="D20" t="n">
-        <v>1.151124221285795</v>
+        <v>1.174987862819212</v>
       </c>
       <c r="E20" t="n">
-        <v>11.22460779297374</v>
+        <v>11.62303375154195</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587622407989224</v>
+        <v>0.7590963115034833</v>
       </c>
       <c r="G20" t="n">
-        <v>19.70935580529932</v>
+        <v>20.09885262934365</v>
       </c>
       <c r="H20" t="n">
-        <v>37.32676378661239</v>
+        <v>37.32910839842615</v>
       </c>
       <c r="I20" t="n">
-        <v>1.115984802983046</v>
+        <v>1.247603687176826</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742264004993267</v>
+        <v>4.744351946896772</v>
       </c>
       <c r="K20" t="n">
-        <v>23.97113734505352</v>
+        <v>23.02296541229195</v>
       </c>
       <c r="L20" t="n">
-        <v>43.16389331291388</v>
+        <v>43.29767249494996</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9628186986791</v>
+        <v>99.9584356655303</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.86441027889769</v>
+        <v>82.74873915845208</v>
       </c>
       <c r="C21" t="n">
-        <v>36.51173949395079</v>
+        <v>37.16358093505845</v>
       </c>
       <c r="D21" t="n">
-        <v>1.151839919198593</v>
+        <v>1.175864345495085</v>
       </c>
       <c r="E21" t="n">
-        <v>13.19391709060059</v>
+        <v>13.54113353931394</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592339922763113</v>
+        <v>0.7596625597068949</v>
       </c>
       <c r="G21" t="n">
-        <v>21.42944923543124</v>
+        <v>21.71464267891034</v>
       </c>
       <c r="H21" t="n">
-        <v>39.05781063244696</v>
+        <v>38.95775136431678</v>
       </c>
       <c r="I21" t="n">
-        <v>1.526946957217058</v>
+        <v>1.851793672540936</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745212451726947</v>
+        <v>4.747890998168094</v>
       </c>
       <c r="K21" t="n">
-        <v>18.13558972110231</v>
+        <v>17.25126084154791</v>
       </c>
       <c r="L21" t="n">
-        <v>45.30180417875236</v>
+        <v>45.52347777819554</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94913339380545</v>
+        <v>99.93831955480189</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_44_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.57021772763912</v>
+        <v>44.82193925051366</v>
       </c>
       <c r="M2" t="n">
-        <v>98.81989387067733</v>
+        <v>101.4203663019007</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92126502156893</v>
+        <v>88.08375408409883</v>
       </c>
       <c r="C3" t="n">
-        <v>45.84317850704044</v>
+        <v>45.9391498674614</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228523207754828</v>
+        <v>2.228867393396386</v>
       </c>
       <c r="E3" t="n">
-        <v>5.651857351819652</v>
+        <v>5.715470205854785</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428410692516095</v>
+        <v>0.7429557977987953</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94452304625181</v>
+        <v>33.97615377792279</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17068918557403</v>
+        <v>34.17596669874458</v>
       </c>
       <c r="I3" t="n">
-        <v>6.54007447809443</v>
+        <v>6.600866474139008</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642756682822559</v>
+        <v>4.643473736242471</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07873497843107</v>
+        <v>11.91624591590118</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84330953018885</v>
+        <v>48.90768149997169</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652230156604</v>
+        <v>106.7630772833343</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.9235784451901</v>
+        <v>87.27233413703445</v>
       </c>
       <c r="C4" t="n">
-        <v>42.47840177621216</v>
+        <v>42.76881423820543</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179920258844079</v>
+        <v>2.190326900761721</v>
       </c>
       <c r="E4" t="n">
-        <v>6.438839315537287</v>
+        <v>6.535358286987442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.74439684544079</v>
+        <v>0.7445200192426175</v>
       </c>
       <c r="G4" t="n">
-        <v>33.20421039719538</v>
+        <v>33.38865462552284</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24225489027634</v>
+        <v>34.2479208851604</v>
       </c>
       <c r="I4" t="n">
-        <v>5.461476453891292</v>
+        <v>5.512303299093042</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652480284004937</v>
+        <v>4.653250120266359</v>
       </c>
       <c r="K4" t="n">
-        <v>13.07642155480993</v>
+        <v>12.72766586296559</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26350793347528</v>
+        <v>44.32016249676956</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81833126449736</v>
+        <v>99.81664259794057</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.735510265575</v>
+        <v>86.25750626201176</v>
       </c>
       <c r="C5" t="n">
-        <v>42.13783703377625</v>
+        <v>42.60962963792156</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121749507379198</v>
+        <v>2.141347866607112</v>
       </c>
       <c r="E5" t="n">
-        <v>7.026903128617128</v>
+        <v>7.156176899520055</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457163792131691</v>
+        <v>0.7458440001022217</v>
       </c>
       <c r="G5" t="n">
-        <v>32.3181624499062</v>
+        <v>32.64203362812231</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30295344380578</v>
+        <v>34.3088240047022</v>
       </c>
       <c r="I5" t="n">
-        <v>4.559297986571219</v>
+        <v>4.601754862318963</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660727370082307</v>
+        <v>4.661525000638886</v>
       </c>
       <c r="K5" t="n">
-        <v>14.264489734425</v>
+        <v>13.74249373798824</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44596555252402</v>
+        <v>43.4947570880043</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84829232072526</v>
+        <v>99.8468804639141</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.30462020189407</v>
+        <v>84.97787397310096</v>
       </c>
       <c r="C6" t="n">
-        <v>41.41487723290299</v>
+        <v>42.04490272520744</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051616624040957</v>
+        <v>2.079139976457986</v>
       </c>
       <c r="E6" t="n">
-        <v>7.428822513244143</v>
+        <v>7.588379636155058</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468383219599513</v>
+        <v>0.746967613450837</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2499091481273</v>
+        <v>31.69375610915959</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35456281015775</v>
+        <v>34.3605102187385</v>
       </c>
       <c r="I6" t="n">
-        <v>3.805131272114281</v>
+        <v>3.840572835071267</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667739512249695</v>
+        <v>4.66854758406773</v>
       </c>
       <c r="K6" t="n">
-        <v>15.69537979810593</v>
+        <v>15.02212602689903</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76309580269743</v>
+        <v>42.80514472394023</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87335283370635</v>
+        <v>99.8721734760467</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.67512507058262</v>
+        <v>83.5316433935684</v>
       </c>
       <c r="C7" t="n">
-        <v>40.37618193052123</v>
+        <v>41.1954256494508</v>
       </c>
       <c r="D7" t="n">
-        <v>1.97205902324757</v>
+        <v>2.009006966117609</v>
       </c>
       <c r="E7" t="n">
-        <v>7.669914574024032</v>
+        <v>7.866505396859337</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747794358446139</v>
+        <v>0.7479228243429827</v>
       </c>
       <c r="G7" t="n">
-        <v>30.03809999835572</v>
+        <v>30.62467054969872</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39854048852239</v>
+        <v>34.40444991977721</v>
       </c>
       <c r="I7" t="n">
-        <v>3.175001887698421</v>
+        <v>3.204570084628904</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673714740288369</v>
+        <v>4.674517652143642</v>
       </c>
       <c r="K7" t="n">
-        <v>17.32487492941736</v>
+        <v>16.46835660643161</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19324504916935</v>
+        <v>42.22953516536563</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89430190910794</v>
+        <v>99.89331742124801</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.56183281743384</v>
+        <v>88.33564349012039</v>
       </c>
       <c r="C8" t="n">
-        <v>42.67102638328367</v>
+        <v>43.4540336804056</v>
       </c>
       <c r="D8" t="n">
-        <v>1.976295357055423</v>
+        <v>2.013273063914645</v>
       </c>
       <c r="E8" t="n">
-        <v>9.49853967575649</v>
+        <v>9.6695837528979</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494007538352535</v>
+        <v>0.7495110278520272</v>
       </c>
       <c r="G8" t="n">
-        <v>30.53845555673773</v>
+        <v>31.11393985991456</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47243467642166</v>
+        <v>34.47750728119326</v>
       </c>
       <c r="I8" t="n">
-        <v>5.642952086156947</v>
+        <v>5.62738458027283</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683754711470335</v>
+        <v>4.68444392407517</v>
       </c>
       <c r="K8" t="n">
-        <v>12.43816718256617</v>
+        <v>11.6643565098796</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70311123397791</v>
+        <v>44.69442780204404</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81230479982776</v>
+        <v>99.81281799232924</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.47131740697789</v>
+        <v>86.45713247178909</v>
       </c>
       <c r="C9" t="n">
-        <v>41.45591927822855</v>
+        <v>42.44937787795238</v>
       </c>
       <c r="D9" t="n">
-        <v>1.881408378286964</v>
+        <v>1.928389567776922</v>
       </c>
       <c r="E9" t="n">
-        <v>9.827673887756671</v>
+        <v>10.0448922182469</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507776297017543</v>
+        <v>0.750868613441391</v>
       </c>
       <c r="G9" t="n">
-        <v>29.07222644594777</v>
+        <v>29.80211582507991</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53577096628069</v>
+        <v>34.539956218304</v>
       </c>
       <c r="I9" t="n">
-        <v>4.711099913368078</v>
+        <v>4.697981194931278</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692360185635965</v>
+        <v>4.692928834008694</v>
       </c>
       <c r="K9" t="n">
-        <v>14.5286825930221</v>
+        <v>13.54286752821091</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85864945968945</v>
+        <v>43.85143835549579</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84325133094009</v>
+        <v>99.84368376165907</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.21875945246325</v>
+        <v>84.31774557806098</v>
       </c>
       <c r="C10" t="n">
-        <v>39.93384781959075</v>
+        <v>41.03937671900193</v>
       </c>
       <c r="D10" t="n">
-        <v>1.780288231589803</v>
+        <v>1.832469695938743</v>
       </c>
       <c r="E10" t="n">
-        <v>9.954815415180878</v>
+        <v>10.19875886558801</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519601085434386</v>
+        <v>0.7520325422591979</v>
       </c>
       <c r="G10" t="n">
-        <v>27.50968009133655</v>
+        <v>28.31973115643451</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59016499299817</v>
+        <v>34.59349694392311</v>
       </c>
       <c r="I10" t="n">
-        <v>3.932099934417912</v>
+        <v>3.921052984797413</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699750678396492</v>
+        <v>4.700203389119988</v>
       </c>
       <c r="K10" t="n">
-        <v>16.78124054753675</v>
+        <v>15.682254421939</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15404774639006</v>
+        <v>43.1478693814221</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86913611351756</v>
+        <v>99.86950052236304</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.88583563125181</v>
+        <v>82.06661379225406</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20994501633058</v>
+        <v>39.39645116674652</v>
       </c>
       <c r="D11" t="n">
-        <v>1.676722375759323</v>
+        <v>1.732537813117125</v>
       </c>
       <c r="E11" t="n">
-        <v>9.922570969221518</v>
+        <v>10.18789428775014</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529768984389555</v>
+        <v>0.7530319601163713</v>
       </c>
       <c r="G11" t="n">
-        <v>25.90934172380279</v>
+        <v>26.77534324009588</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63693732819195</v>
+        <v>34.63947016535309</v>
       </c>
       <c r="I11" t="n">
-        <v>3.281180720593797</v>
+        <v>3.271886575094141</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706105615243472</v>
+        <v>4.706449750727321</v>
       </c>
       <c r="K11" t="n">
-        <v>19.11416436874821</v>
+        <v>17.93338620774593</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56666561674292</v>
+        <v>42.56124448704095</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89077500182171</v>
+        <v>99.89108186153339</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.5605766533097</v>
+        <v>79.6939880268134</v>
       </c>
       <c r="C12" t="n">
-        <v>36.3920725338074</v>
+        <v>37.53061022662413</v>
       </c>
       <c r="D12" t="n">
-        <v>1.57460475892369</v>
+        <v>1.628164326345829</v>
       </c>
       <c r="E12" t="n">
-        <v>9.774504353947282</v>
+        <v>10.0290912583266</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538514970621252</v>
+        <v>0.7538917239146844</v>
       </c>
       <c r="G12" t="n">
-        <v>24.33138208727287</v>
+        <v>25.16231297183349</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67716886485776</v>
+        <v>34.67901930007549</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737493234607678</v>
+        <v>2.729685171850526</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711571856638282</v>
+        <v>4.711823274466778</v>
       </c>
       <c r="K12" t="n">
-        <v>21.43942334669031</v>
+        <v>20.3060119731866</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07736021059692</v>
+        <v>42.07249206199219</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90885609109463</v>
+        <v>99.90911426180293</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.22848246976903</v>
+        <v>77.20547371868696</v>
       </c>
       <c r="C13" t="n">
-        <v>34.48245590736082</v>
+        <v>35.46406891282895</v>
       </c>
       <c r="D13" t="n">
-        <v>1.473157372782266</v>
+        <v>1.519614455414854</v>
       </c>
       <c r="E13" t="n">
-        <v>9.525347389454684</v>
+        <v>9.739946436144956</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546042501169229</v>
+        <v>0.7546328595232011</v>
       </c>
       <c r="G13" t="n">
-        <v>22.76377910628775</v>
+        <v>23.48473916603254</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71179550537845</v>
+        <v>34.71311153806726</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283522282518197</v>
+        <v>2.276973891484136</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716276563230768</v>
+        <v>4.716455372020008</v>
       </c>
       <c r="K13" t="n">
-        <v>23.77151753023097</v>
+        <v>22.79452628131305</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6699850836691</v>
+        <v>41.66558021775104</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92395852126089</v>
+        <v>99.92417541189305</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.37382773922306</v>
+        <v>83.79851216112618</v>
       </c>
       <c r="C14" t="n">
-        <v>38.85542534288306</v>
+        <v>39.53767772532312</v>
       </c>
       <c r="D14" t="n">
-        <v>1.474970588572871</v>
+        <v>1.521405733443643</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96555902655269</v>
+        <v>12.02012860831741</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555330445330865</v>
+        <v>0.7555223991404699</v>
       </c>
       <c r="G14" t="n">
-        <v>24.70718735700611</v>
+        <v>25.28722686735877</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66990981018276</v>
+        <v>36.52883492339046</v>
       </c>
       <c r="I14" t="n">
-        <v>3.078586384043751</v>
+        <v>2.963378634847485</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722081528331791</v>
+        <v>4.722014994627938</v>
       </c>
       <c r="K14" t="n">
-        <v>16.62617226077692</v>
+        <v>16.20148783887383</v>
       </c>
       <c r="L14" t="n">
-        <v>44.41590900280984</v>
+        <v>44.16217144907982</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89750660646983</v>
+        <v>99.90133701327677</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.73256977376315</v>
+        <v>82.89138709987914</v>
       </c>
       <c r="C15" t="n">
-        <v>38.68717802903477</v>
+        <v>39.08873891296432</v>
       </c>
       <c r="D15" t="n">
-        <v>1.451398906929861</v>
+        <v>1.487339373572394</v>
       </c>
       <c r="E15" t="n">
-        <v>12.20475780547781</v>
+        <v>12.16297094793177</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563148072099375</v>
+        <v>0.7562734235914559</v>
       </c>
       <c r="G15" t="n">
-        <v>24.31473677953524</v>
+        <v>24.72101119479159</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71025072216306</v>
+        <v>36.56514628652769</v>
       </c>
       <c r="I15" t="n">
-        <v>2.568143207385135</v>
+        <v>2.471936976017662</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72696754506211</v>
+        <v>4.7267088974466</v>
       </c>
       <c r="K15" t="n">
-        <v>17.26743022623685</v>
+        <v>17.10861290012085</v>
       </c>
       <c r="L15" t="n">
-        <v>43.9598754562827</v>
+        <v>43.72033211372464</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91448371155433</v>
+        <v>99.91768392680981</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.49319344289914</v>
+        <v>80.27874047438345</v>
       </c>
       <c r="C16" t="n">
-        <v>36.8445185248701</v>
+        <v>36.85827289439396</v>
       </c>
       <c r="D16" t="n">
-        <v>1.367012535647483</v>
+        <v>1.387255194461802</v>
       </c>
       <c r="E16" t="n">
-        <v>11.85215899361136</v>
+        <v>11.68813402149051</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569856878318265</v>
+        <v>0.7569208416463923</v>
       </c>
       <c r="G16" t="n">
-        <v>22.90104382736721</v>
+        <v>23.0575158579662</v>
       </c>
       <c r="H16" t="n">
-        <v>36.74281414099264</v>
+        <v>36.59644837271613</v>
       </c>
       <c r="I16" t="n">
-        <v>2.142017708499703</v>
+        <v>2.061710925812468</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731160548948917</v>
+        <v>4.730755260289953</v>
       </c>
       <c r="K16" t="n">
-        <v>19.50680655710087</v>
+        <v>19.72125952561655</v>
       </c>
       <c r="L16" t="n">
-        <v>43.57733760671278</v>
+        <v>43.35180266398901</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92866268868374</v>
+        <v>99.93133508399951</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.37852209918064</v>
+        <v>81.73868766789185</v>
       </c>
       <c r="C17" t="n">
-        <v>38.20051749933904</v>
+        <v>37.93929259992605</v>
       </c>
       <c r="D17" t="n">
-        <v>1.368202753291588</v>
+        <v>1.38841588160253</v>
       </c>
       <c r="E17" t="n">
-        <v>12.70402403007203</v>
+        <v>12.39405819884996</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576447730256326</v>
+        <v>0.7575541413384428</v>
       </c>
       <c r="G17" t="n">
-        <v>23.40390601098576</v>
+        <v>23.4310073834775</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25772794727252</v>
+        <v>36.98126763729937</v>
       </c>
       <c r="I17" t="n">
-        <v>2.151736753122887</v>
+        <v>2.05167104195877</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735279831410205</v>
+        <v>4.734713383365269</v>
       </c>
       <c r="K17" t="n">
-        <v>17.62147790081938</v>
+        <v>18.26131233210815</v>
       </c>
       <c r="L17" t="n">
-        <v>44.10634243554475</v>
+        <v>43.73106320506128</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92833783570318</v>
+        <v>99.93166813709547</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.19093295971561</v>
+        <v>79.18326711607669</v>
       </c>
       <c r="C18" t="n">
-        <v>36.34504075473264</v>
+        <v>35.70056936483645</v>
       </c>
       <c r="D18" t="n">
-        <v>1.289297822963414</v>
+        <v>1.294005792726876</v>
       </c>
       <c r="E18" t="n">
-        <v>12.2704519162426</v>
+        <v>11.83644135082694</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7582099062304321</v>
+        <v>0.7580997712578597</v>
       </c>
       <c r="G18" t="n">
-        <v>22.05419116151534</v>
+        <v>21.83773585811367</v>
       </c>
       <c r="H18" t="n">
-        <v>37.28551878005858</v>
+        <v>37.0079034709379</v>
       </c>
       <c r="I18" t="n">
-        <v>1.794451458765055</v>
+        <v>1.710957301851825</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738811913940201</v>
+        <v>4.738123570361624</v>
       </c>
       <c r="K18" t="n">
-        <v>19.80906704028438</v>
+        <v>20.8167328839233</v>
       </c>
       <c r="L18" t="n">
-        <v>43.78612173961847</v>
+        <v>43.42570688896361</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94022953463549</v>
+        <v>99.94300913772337</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.36068856118816</v>
+        <v>78.06805081143754</v>
       </c>
       <c r="C19" t="n">
-        <v>35.79113577769726</v>
+        <v>34.84869942687671</v>
       </c>
       <c r="D19" t="n">
-        <v>1.260032687558244</v>
+        <v>1.253500063437477</v>
       </c>
       <c r="E19" t="n">
-        <v>12.24131698676831</v>
+        <v>11.70370782605247</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586864316847162</v>
+        <v>0.7585615715170927</v>
       </c>
       <c r="G19" t="n">
-        <v>21.55359395340885</v>
+        <v>21.1541582250506</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30895226283015</v>
+        <v>37.03044702003857</v>
       </c>
       <c r="I19" t="n">
-        <v>1.496316040908394</v>
+        <v>1.4266662833595</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741790198029477</v>
+        <v>4.74100982198183</v>
       </c>
       <c r="K19" t="n">
-        <v>20.63931143881182</v>
+        <v>21.93194918856247</v>
       </c>
       <c r="L19" t="n">
-        <v>43.51970690963633</v>
+        <v>43.17182479284271</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95015412614543</v>
+        <v>99.95247340828189</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.97703458770803</v>
+        <v>75.26733077823927</v>
       </c>
       <c r="C20" t="n">
-        <v>33.63779775828839</v>
+        <v>32.26735574777043</v>
       </c>
       <c r="D20" t="n">
-        <v>1.174987862819212</v>
+        <v>1.151187329618655</v>
       </c>
       <c r="E20" t="n">
-        <v>11.62303375154195</v>
+        <v>10.94668445057129</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590963115034833</v>
+        <v>0.7589611783851813</v>
       </c>
       <c r="G20" t="n">
-        <v>20.09885262934365</v>
+        <v>19.42752108894582</v>
       </c>
       <c r="H20" t="n">
-        <v>37.32910839842615</v>
+        <v>37.04995449512461</v>
       </c>
       <c r="I20" t="n">
-        <v>1.247603687176826</v>
+        <v>1.189514870686335</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744351946896772</v>
+        <v>4.743507364907384</v>
       </c>
       <c r="K20" t="n">
-        <v>23.02296541229195</v>
+        <v>24.73266922176073</v>
       </c>
       <c r="L20" t="n">
-        <v>43.29767249494996</v>
+        <v>42.96034541148664</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9584356655303</v>
+        <v>99.9603703810178</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.74873915845208</v>
+        <v>81.26618231531489</v>
       </c>
       <c r="C21" t="n">
-        <v>37.16358093505845</v>
+        <v>35.98699722875409</v>
       </c>
       <c r="D21" t="n">
-        <v>1.175864345495085</v>
+        <v>1.15200026616776</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54113353931394</v>
+        <v>12.95051344539172</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596625597068949</v>
+        <v>0.7594971357097514</v>
       </c>
       <c r="G21" t="n">
-        <v>21.71464267891034</v>
+        <v>21.15039940036294</v>
       </c>
       <c r="H21" t="n">
-        <v>38.95775136431678</v>
+        <v>38.78527728002705</v>
       </c>
       <c r="I21" t="n">
-        <v>1.851793672540936</v>
+        <v>1.721637689469731</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747890998168094</v>
+        <v>4.746857098185948</v>
       </c>
       <c r="K21" t="n">
-        <v>17.25126084154791</v>
+        <v>18.7338176846851</v>
       </c>
       <c r="L21" t="n">
-        <v>45.52347777819554</v>
+        <v>45.22183766073933</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93831955480189</v>
+        <v>99.94265257417852</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_44_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.82193925051366</v>
+        <v>43.18773928638746</v>
       </c>
       <c r="M2" t="n">
-        <v>101.4203663019007</v>
+        <v>96.47985735266261</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08375408409883</v>
+        <v>81.57032344031606</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9391498674614</v>
+        <v>43.32587899587162</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228867393396386</v>
+        <v>2.18551476142687</v>
       </c>
       <c r="E3" t="n">
-        <v>5.715470205854785</v>
+        <v>4.154815466862444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429557977987953</v>
+        <v>0.7376988448574326</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97615377792279</v>
+        <v>32.87378453646249</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17596669874458</v>
+        <v>33.9341468634419</v>
       </c>
       <c r="I3" t="n">
-        <v>6.600866474139008</v>
+        <v>3.073745186905969</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643473736242471</v>
+        <v>4.610617780358954</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91624591590118</v>
+        <v>18.42967655968394</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90768149997169</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7630772833343</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.27233413703445</v>
+        <v>88.81090565340352</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76881423820543</v>
+        <v>42.97596344323663</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190326900761721</v>
+        <v>2.191317264434456</v>
       </c>
       <c r="E4" t="n">
-        <v>6.535358286987442</v>
+        <v>6.580284664559241</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445200192426175</v>
+        <v>0.7396574222331277</v>
       </c>
       <c r="G4" t="n">
-        <v>33.38865462552284</v>
+        <v>33.57880451426936</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2479208851604</v>
+        <v>34.02424142272387</v>
       </c>
       <c r="I4" t="n">
-        <v>5.512303299093042</v>
+        <v>7.073741476226421</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653250120266359</v>
+        <v>4.622858888957047</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72766586296559</v>
+        <v>11.18909434659647</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32016249676956</v>
+        <v>45.59977519189702</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81664259794057</v>
+        <v>99.76483298173014</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.25750626201176</v>
+        <v>87.95403339047775</v>
       </c>
       <c r="C5" t="n">
-        <v>42.60962963792156</v>
+        <v>43.21565569649075</v>
       </c>
       <c r="D5" t="n">
-        <v>2.141347866607112</v>
+        <v>2.151787703429612</v>
       </c>
       <c r="E5" t="n">
-        <v>7.156176899520055</v>
+        <v>7.446245614042236</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458440001022217</v>
+        <v>0.7413135462639785</v>
       </c>
       <c r="G5" t="n">
-        <v>32.64203362812231</v>
+        <v>32.97307050073339</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3088240047022</v>
+        <v>34.10042312814301</v>
       </c>
       <c r="I5" t="n">
-        <v>4.601754862318963</v>
+        <v>5.907983233715664</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661525000638886</v>
+        <v>4.633209664149866</v>
       </c>
       <c r="K5" t="n">
-        <v>13.74249373798824</v>
+        <v>12.04596660952224</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4947570880043</v>
+        <v>44.54188487520293</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8468804639141</v>
+        <v>99.80350718121592</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.97787397310096</v>
+        <v>86.84008810041539</v>
       </c>
       <c r="C6" t="n">
-        <v>42.04490272520744</v>
+        <v>43.0190253013118</v>
       </c>
       <c r="D6" t="n">
-        <v>2.079139976457986</v>
+        <v>2.099450067454093</v>
       </c>
       <c r="E6" t="n">
-        <v>7.588379636155058</v>
+        <v>8.087238454198218</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746967613450837</v>
+        <v>0.7427171352176787</v>
       </c>
       <c r="G6" t="n">
-        <v>31.69375610915959</v>
+        <v>32.17107104785428</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3605102187385</v>
+        <v>34.16498822001321</v>
       </c>
       <c r="I6" t="n">
-        <v>3.840572835071267</v>
+        <v>4.932641080567415</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66854758406773</v>
+        <v>4.641982095110492</v>
       </c>
       <c r="K6" t="n">
-        <v>15.02212602689903</v>
+        <v>13.15991189958461</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80514472394023</v>
+        <v>43.65695215372259</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8721734760467</v>
+        <v>99.83588935461901</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.5316433935684</v>
+        <v>85.45001248476021</v>
       </c>
       <c r="C7" t="n">
-        <v>41.1954256494508</v>
+        <v>42.39549012803678</v>
       </c>
       <c r="D7" t="n">
-        <v>2.009006966117609</v>
+        <v>2.033812560550383</v>
       </c>
       <c r="E7" t="n">
-        <v>7.866505396859337</v>
+        <v>8.52058720879041</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479228243429827</v>
+        <v>0.7439099836701747</v>
       </c>
       <c r="G7" t="n">
-        <v>30.62467054969872</v>
+        <v>31.16527008562233</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40444991977721</v>
+        <v>34.21985924882803</v>
       </c>
       <c r="I7" t="n">
-        <v>3.204570084628904</v>
+        <v>4.11713599936029</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674517652143642</v>
+        <v>4.649437397938593</v>
       </c>
       <c r="K7" t="n">
-        <v>16.46835660643161</v>
+        <v>14.54998751523979</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22953516536563</v>
+        <v>42.91750454892988</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89331742124801</v>
+        <v>99.86298219220646</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.33564349012039</v>
+        <v>83.96494096042055</v>
       </c>
       <c r="C8" t="n">
-        <v>43.4540336804056</v>
+        <v>41.55033275864921</v>
       </c>
       <c r="D8" t="n">
-        <v>2.013273063914645</v>
+        <v>1.96409128439096</v>
       </c>
       <c r="E8" t="n">
-        <v>9.6695837528979</v>
+        <v>8.801096702739642</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495110278520272</v>
+        <v>0.7449246121509614</v>
       </c>
       <c r="G8" t="n">
-        <v>31.11393985991456</v>
+        <v>30.09689119743478</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47750728119326</v>
+        <v>34.26653215894422</v>
       </c>
       <c r="I8" t="n">
-        <v>5.62738458027283</v>
+        <v>3.435626178816474</v>
       </c>
       <c r="J8" t="n">
-        <v>4.68444392407517</v>
+        <v>4.65577882594351</v>
       </c>
       <c r="K8" t="n">
-        <v>11.6643565098796</v>
+        <v>16.03505903957947</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69442780204404</v>
+        <v>42.30024331290019</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81281799232924</v>
+        <v>99.88563511112886</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.45713247178909</v>
+        <v>82.20156443265289</v>
       </c>
       <c r="C9" t="n">
-        <v>42.44937787795238</v>
+        <v>40.32079757156212</v>
       </c>
       <c r="D9" t="n">
-        <v>1.928389567776922</v>
+        <v>1.881516594745169</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0448922182469</v>
+        <v>8.908804294563161</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750868613441391</v>
+        <v>0.7457904571274403</v>
       </c>
       <c r="G9" t="n">
-        <v>29.80211582507991</v>
+        <v>28.83155212196409</v>
       </c>
       <c r="H9" t="n">
-        <v>34.539956218304</v>
+        <v>34.30636102786224</v>
       </c>
       <c r="I9" t="n">
-        <v>4.697981194931278</v>
+        <v>2.866349579344289</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692928834008694</v>
+        <v>4.661190357046503</v>
       </c>
       <c r="K9" t="n">
-        <v>13.54286752821091</v>
+        <v>17.7984355673471</v>
       </c>
       <c r="L9" t="n">
-        <v>43.85143835549579</v>
+        <v>41.78533280056812</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84368376165907</v>
+        <v>99.90456593947734</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.31774557806098</v>
+        <v>86.52400086774799</v>
       </c>
       <c r="C10" t="n">
-        <v>41.03937671900193</v>
+        <v>43.28432434671986</v>
       </c>
       <c r="D10" t="n">
-        <v>1.832469695938743</v>
+        <v>1.883665982887891</v>
       </c>
       <c r="E10" t="n">
-        <v>10.19875886558801</v>
+        <v>10.62608389826763</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520325422591979</v>
+        <v>0.7466424257839923</v>
       </c>
       <c r="G10" t="n">
-        <v>28.31973115643451</v>
+        <v>30.07737875408327</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59349694392311</v>
+        <v>35.55844191751967</v>
       </c>
       <c r="I10" t="n">
-        <v>3.921052984797413</v>
+        <v>2.965272728055568</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700203389119988</v>
+        <v>4.666515161149952</v>
       </c>
       <c r="K10" t="n">
-        <v>15.682254421939</v>
+        <v>13.47599913225201</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1478693814221</v>
+        <v>43.14094688253832</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86950052236304</v>
+        <v>99.9012703615102</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.06661379225406</v>
+        <v>86.27058233285075</v>
       </c>
       <c r="C11" t="n">
-        <v>39.39645116674652</v>
+        <v>43.39629148171911</v>
       </c>
       <c r="D11" t="n">
-        <v>1.732537813117125</v>
+        <v>1.865296254119492</v>
       </c>
       <c r="E11" t="n">
-        <v>10.18789428775014</v>
+        <v>10.9919690734649</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530319601163713</v>
+        <v>0.7473688843381792</v>
       </c>
       <c r="G11" t="n">
-        <v>26.77534324009588</v>
+        <v>29.83388043590416</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63947016535309</v>
+        <v>35.6428588754512</v>
       </c>
       <c r="I11" t="n">
-        <v>3.271886575094141</v>
+        <v>2.518153282459191</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706449750727321</v>
+        <v>4.67105552711362</v>
       </c>
       <c r="K11" t="n">
-        <v>17.93338620774593</v>
+        <v>13.72941766714924</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56124448704095</v>
+        <v>42.79043399834618</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89108186153339</v>
+        <v>99.91614314721454</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.6939880268134</v>
+        <v>84.39734880828556</v>
       </c>
       <c r="C12" t="n">
-        <v>37.53061022662413</v>
+        <v>41.91502463471424</v>
       </c>
       <c r="D12" t="n">
-        <v>1.628164326345829</v>
+        <v>1.784928764541534</v>
       </c>
       <c r="E12" t="n">
-        <v>10.0290912583266</v>
+        <v>10.86840663177412</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538917239146844</v>
+        <v>0.7479888190631447</v>
       </c>
       <c r="G12" t="n">
-        <v>25.16231297183349</v>
+        <v>28.54846849680478</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67901930007549</v>
+        <v>35.67242425658626</v>
       </c>
       <c r="I12" t="n">
-        <v>2.729685171850526</v>
+        <v>2.100201720371082</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711823274466778</v>
+        <v>4.674930119144655</v>
       </c>
       <c r="K12" t="n">
-        <v>20.3060119731866</v>
+        <v>15.60265119171441</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07249206199219</v>
+        <v>42.41237547128082</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90911426180293</v>
+        <v>99.93005129770947</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.20547371868696</v>
+        <v>85.46846500604998</v>
       </c>
       <c r="C13" t="n">
-        <v>35.46406891282895</v>
+        <v>42.83047438617733</v>
       </c>
       <c r="D13" t="n">
-        <v>1.519614455414854</v>
+        <v>1.786285643833325</v>
       </c>
       <c r="E13" t="n">
-        <v>9.739946436144956</v>
+        <v>11.47977422736799</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546328595232011</v>
+        <v>0.7485574302924778</v>
       </c>
       <c r="G13" t="n">
-        <v>23.48473916603254</v>
+        <v>28.84841624609472</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71311153806726</v>
+        <v>35.9777875430327</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276973891484136</v>
+        <v>1.949159976100776</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716455372020008</v>
+        <v>4.678483939327986</v>
       </c>
       <c r="K13" t="n">
-        <v>22.79452628131305</v>
+        <v>14.53153499395001</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66558021775104</v>
+        <v>42.57306797400791</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92417541189305</v>
+        <v>99.93507735413526</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.79851216112618</v>
+        <v>83.49129385203621</v>
       </c>
       <c r="C14" t="n">
-        <v>39.53767772532312</v>
+        <v>41.15657905692207</v>
       </c>
       <c r="D14" t="n">
-        <v>1.521405733443643</v>
+        <v>1.703528645382455</v>
       </c>
       <c r="E14" t="n">
-        <v>12.02012860831741</v>
+        <v>11.21881900367454</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555223991404699</v>
+        <v>0.7490431778727612</v>
       </c>
       <c r="G14" t="n">
-        <v>25.28722686735877</v>
+        <v>27.51189521048656</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52883492339046</v>
+        <v>36.00113394577451</v>
       </c>
       <c r="I14" t="n">
-        <v>2.963378634847485</v>
+        <v>1.625354007140624</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722014994627938</v>
+        <v>4.681519861704758</v>
       </c>
       <c r="K14" t="n">
-        <v>16.20148783887383</v>
+        <v>16.50870614796379</v>
       </c>
       <c r="L14" t="n">
-        <v>44.16217144907982</v>
+        <v>42.28057146244467</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90133701327677</v>
+        <v>99.94585666733053</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.89138709987914</v>
+        <v>82.56917750334534</v>
       </c>
       <c r="C15" t="n">
-        <v>39.08873891296432</v>
+        <v>40.46985325280546</v>
       </c>
       <c r="D15" t="n">
-        <v>1.487339373572394</v>
+        <v>1.664765813645912</v>
       </c>
       <c r="E15" t="n">
-        <v>12.16297094793177</v>
+        <v>11.19216288311909</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562734235914559</v>
+        <v>0.7494579756938655</v>
       </c>
       <c r="G15" t="n">
-        <v>24.72101119479159</v>
+        <v>26.88587758073426</v>
       </c>
       <c r="H15" t="n">
-        <v>36.56514628652769</v>
+        <v>36.0210703023947</v>
       </c>
       <c r="I15" t="n">
-        <v>2.471936976017662</v>
+        <v>1.371730599670873</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7267088974466</v>
+        <v>4.68411234808666</v>
       </c>
       <c r="K15" t="n">
-        <v>17.10861290012085</v>
+        <v>17.43082249665465</v>
       </c>
       <c r="L15" t="n">
-        <v>43.72033211372464</v>
+        <v>42.05362520398954</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91768392680981</v>
+        <v>99.95430095344966</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.27874047438345</v>
+        <v>80.27551052443648</v>
       </c>
       <c r="C16" t="n">
-        <v>36.85827289439396</v>
+        <v>38.38911541312743</v>
       </c>
       <c r="D16" t="n">
-        <v>1.387255194461802</v>
+        <v>1.569432534264694</v>
       </c>
       <c r="E16" t="n">
-        <v>11.68813402149051</v>
+        <v>10.74184916227191</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569208416463923</v>
+        <v>0.7498138828553574</v>
       </c>
       <c r="G16" t="n">
-        <v>23.0575158579662</v>
+        <v>25.34625029033475</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59644837271613</v>
+        <v>36.03817620733001</v>
       </c>
       <c r="I16" t="n">
-        <v>2.061710925812468</v>
+        <v>1.143651679533773</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730755260289953</v>
+        <v>4.686336767845985</v>
       </c>
       <c r="K16" t="n">
-        <v>19.72125952561655</v>
+        <v>19.72448947556352</v>
       </c>
       <c r="L16" t="n">
-        <v>43.35180266398901</v>
+        <v>41.84829148354042</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93133508399951</v>
+        <v>99.96189637223137</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.73868766789185</v>
+        <v>84.78938030154541</v>
       </c>
       <c r="C17" t="n">
-        <v>37.93929259992605</v>
+        <v>41.34196211376029</v>
       </c>
       <c r="D17" t="n">
-        <v>1.38841588160253</v>
+        <v>1.570248425647342</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39405819884996</v>
+        <v>12.32570173844296</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575541413384428</v>
+        <v>0.7502036840556352</v>
       </c>
       <c r="G17" t="n">
-        <v>23.4310073834775</v>
+        <v>26.7173004609741</v>
       </c>
       <c r="H17" t="n">
-        <v>36.98126763729937</v>
+        <v>37.41478472471516</v>
       </c>
       <c r="I17" t="n">
-        <v>2.05167104195877</v>
+        <v>1.322368242362505</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734713383365269</v>
+        <v>4.688773025347721</v>
       </c>
       <c r="K17" t="n">
-        <v>18.26131233210815</v>
+        <v>15.21061969845458</v>
       </c>
       <c r="L17" t="n">
-        <v>43.73106320506128</v>
+        <v>43.40336214951874</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93166813709547</v>
+        <v>99.95594396173361</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.18326711607669</v>
+        <v>86.34748263052441</v>
       </c>
       <c r="C18" t="n">
-        <v>35.70056936483645</v>
+        <v>42.06755077232506</v>
       </c>
       <c r="D18" t="n">
-        <v>1.294005792726876</v>
+        <v>1.571526169480081</v>
       </c>
       <c r="E18" t="n">
-        <v>11.83644135082694</v>
+        <v>12.92261559291389</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580997712578597</v>
+        <v>0.750814140410785</v>
       </c>
       <c r="G18" t="n">
-        <v>21.83773585811367</v>
+        <v>26.85682611132884</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0079034709379</v>
+        <v>37.44522991393136</v>
       </c>
       <c r="I18" t="n">
-        <v>1.710957301851825</v>
+        <v>2.107882324892045</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738123570361624</v>
+        <v>4.692588377567406</v>
       </c>
       <c r="K18" t="n">
-        <v>20.8167328839233</v>
+        <v>13.65251736947559</v>
       </c>
       <c r="L18" t="n">
-        <v>43.42570688896361</v>
+        <v>44.20972624180784</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94300913772337</v>
+        <v>99.9297943836085</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.06805081143754</v>
+        <v>83.82335037804361</v>
       </c>
       <c r="C19" t="n">
-        <v>34.84869942687671</v>
+        <v>39.87041119566557</v>
       </c>
       <c r="D19" t="n">
-        <v>1.253500063437477</v>
+        <v>1.476629038103781</v>
       </c>
       <c r="E19" t="n">
-        <v>11.70370782605247</v>
+        <v>12.43524522119952</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585615715170927</v>
+        <v>0.7513389657059749</v>
       </c>
       <c r="G19" t="n">
-        <v>21.1541582250506</v>
+        <v>25.23506771790647</v>
       </c>
       <c r="H19" t="n">
-        <v>37.03044702003857</v>
+        <v>37.47140443940351</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4266662833595</v>
+        <v>1.75779646006201</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74100982198183</v>
+        <v>4.695868535662344</v>
       </c>
       <c r="K19" t="n">
-        <v>21.93194918856247</v>
+        <v>16.17664962195639</v>
       </c>
       <c r="L19" t="n">
-        <v>43.17182479284271</v>
+        <v>43.89438689557547</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95247340828189</v>
+        <v>99.94144771319742</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.26733077823927</v>
+        <v>81.21653533391114</v>
       </c>
       <c r="C20" t="n">
-        <v>32.26735574777043</v>
+        <v>37.53560429601411</v>
       </c>
       <c r="D20" t="n">
-        <v>1.151187329618655</v>
+        <v>1.379128686577423</v>
       </c>
       <c r="E20" t="n">
-        <v>10.94668445057129</v>
+        <v>11.85844356938118</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589611783851813</v>
+        <v>0.751790945184428</v>
       </c>
       <c r="G20" t="n">
-        <v>19.42752108894582</v>
+        <v>23.56882121333625</v>
       </c>
       <c r="H20" t="n">
-        <v>37.04995449512461</v>
+        <v>37.49394593746027</v>
       </c>
       <c r="I20" t="n">
-        <v>1.189514870686335</v>
+        <v>1.465711574568914</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743507364907384</v>
+        <v>4.698693407402676</v>
       </c>
       <c r="K20" t="n">
-        <v>24.73266922176073</v>
+        <v>18.78346466608886</v>
       </c>
       <c r="L20" t="n">
-        <v>42.96034541148664</v>
+        <v>43.63210335845086</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9603703810178</v>
+        <v>99.95117232055384</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.26618231531489</v>
+        <v>78.59712446673318</v>
       </c>
       <c r="C21" t="n">
-        <v>35.98699722875409</v>
+        <v>35.14234459932478</v>
       </c>
       <c r="D21" t="n">
-        <v>1.15200026616776</v>
+        <v>1.281643756922312</v>
       </c>
       <c r="E21" t="n">
-        <v>12.95051344539172</v>
+        <v>11.22389556769351</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594971357097514</v>
+        <v>0.7521805833390064</v>
       </c>
       <c r="G21" t="n">
-        <v>21.15039940036294</v>
+        <v>21.90283826308819</v>
       </c>
       <c r="H21" t="n">
-        <v>38.78527728002705</v>
+        <v>37.51337829694334</v>
       </c>
       <c r="I21" t="n">
-        <v>1.721637689469731</v>
+        <v>1.222059352878036</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746857098185948</v>
+        <v>4.701128645868791</v>
       </c>
       <c r="K21" t="n">
-        <v>18.7338176846851</v>
+        <v>21.40287553326682</v>
       </c>
       <c r="L21" t="n">
-        <v>45.22183766073933</v>
+        <v>43.41406565700372</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94265257417852</v>
+        <v>99.95928578959531</v>
       </c>
     </row>
   </sheetData>
